--- a/Week 1/Group Work/Apollo249/apollo-test-scenario-document.xlsx
+++ b/Week 1/Group Work/Apollo249/apollo-test-scenario-document.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\308345\Documents\Testing\Group Work\Apollo249\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\308345\Documents\Testing\Week 1\Group Work\Apollo249\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3B9F22-6FB8-475C-8B10-0CE3CF7B9D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2920889B-DB78-461B-B70D-1A2E66CCF285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{67B174C0-A3F8-404A-8057-880177842696}"/>
+    <workbookView xWindow="2964" yWindow="2964" windowWidth="17280" windowHeight="8880" xr2:uid="{67B174C0-A3F8-404A-8057-880177842696}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -558,7 +558,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4498443-BBA0-405C-925A-D66E72C899F6}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="20.44140625" customWidth="1"/>
@@ -568,7 +568,7 @@
     <col min="6" max="6" width="44.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6">
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -588,7 +588,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="158.4" customHeight="1">
+    <row r="2" spans="1:6" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -608,7 +608,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="201.6">
+    <row r="3" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -628,10 +628,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="4"/>
